--- a/Test Files/intake_bypass_scenarios.xlsx
+++ b/Test Files/intake_bypass_scenarios.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,29 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +66,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,17 +448,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>intake-bypass scenarios</t>
+          <t>intake-bypass scenarios — exhaustive override sheet</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -440,7 +470,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Each non-underscore sheet is one scenario.</t>
+          <t>Each non-underscore sheet is ONE scenario. Sheets starting with '_' are ignored.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -448,35 +478,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Column A = field name, Column B = value.</t>
+          <t>Column A = field path, Column B = value.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Rows whose field starts with '#' are comments and are ignored.</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sheets whose name starts with '_' (like this one) are ignored.</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Every leaf of the baseline is listed and PRE-FILLED with the baseline value.</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Required field:</t>
+          <t>To build a scenario, edit only the cells you want to change.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -484,31 +514,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>baseline</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>name of a captured baseline snapshot (file in intake_bypass_baselines/)</t>
-        </is>
-      </c>
+          <t>A row is applied only when its value DIFFERS from the baseline at that path,</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>so an unedited sheet reproduces the baseline exactly.</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Override fields (blank cell = inherit the baseline value):</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Financial scalars (financials_json):</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CONVENTIONS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -516,47 +542,59 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  cash_on_hand, ar_balance, ap_balance, inventory_balance</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>REQUIRED. Name of the baseline snapshot in intake_bypass_baselines/.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  current_capex, initial_assets, initial_lease, initial_equity</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>blank cell</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>inherit the baseline value (no change).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  total_debt_outstanding, annual_interest_payment, annual_principal_payment</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>(null)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>explicitly set the field to null.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  other_monthly_debt_payments, monthly_rent_expense, other_operating_expense</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>rows starting with #</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>comments / section headers — ignored.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  owner_compensation, current_payroll, payroll_total_year1, current_num_employees</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  current_cogs, current_revenue, cogs_percent_of_revenue (accepts 29% or 0.29)</t>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>PATH SYNTAX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -564,67 +602,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Shape-affecting (operating_model_json + financials_year1_json; solver re-derives revenue):</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>draft.&lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>a flat draft column, e.g. draft.business_name, draft.address_city.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  unit_price, units_per_week_capacity, utilization_rate</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>&lt;payload&gt;.&lt;path&gt;</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>a leaf inside a structured JSON column.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Descriptors (operating_model_json):</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>list items use [i]</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>e.g. operating_model_json.lob_models[0].products[0].unit_price</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  naics, business_stage</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>payloads exposed</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>operating_model_json, target_market_json, people_json, financials_json, financials_year1_json, marketing_model_json, fulfillment_json</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Flat draft columns:</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  business_name, business_start_date, business_address,</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>NUMBERS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>plain (20000), separated ($20,000), or percent (29%) all parse.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  address_street, address_city, address_state, address_zip, address_country</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DENORMALIZATION — edit consistently</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Numbers may be written plainly (20000), with separators ($20,000), or percents (29%).</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>unit_price / units_per_week_capacity / utilization_rate appear in BOTH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -632,10 +686,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>An unknown field name fails loudly so typos are caught.</t>
+          <t>operating_model_json (top-level AND each product) and financials_year1_json</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>products. To change price/capacity/util coherently, edit every occurrence.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LIMITATION</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Editing existing leaves is supported. To ADD a brand-new array element</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>(e.g. a 3rd product or an 8th person), edit the baseline JSON in</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>intake_bypass_baselines/ directly, or capture a baseline that already has it.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>(For headcount scale, financials_json.current_num_employees / payroll_total_year1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> are usually the right knobs — post-intake authors the full headcount grid.)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -648,142 +762,2832 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>sunny_glaze_donuts</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>business_name</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sunny Glaze Donuts</t>
-        </is>
-      </c>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t># ===== draft (business identity / address) =====</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t># --- financial overrides: fill a value to change it, leave blank to inherit ---</t>
+          <t>draft.business_name</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Sunny Glaze Donuts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cash_on_hand</t>
+          <t>draft.business_address</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>457 Maple Avenue, Springfield, IL 62704, USA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>current_capex</t>
+          <t>draft.address_street</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>457 Maple Avenue</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>total_debt_outstanding</t>
+          <t>draft.address_city</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Springfield</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>payroll_total_year1</t>
+          <t>draft.address_state</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>IL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>monthly_rent_expense</t>
+          <t>draft.address_zip</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>62704</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>other_operating_expense</t>
+          <t>draft.address_country</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t># --- shape-affecting overrides (optional) ---</t>
+          <t>draft.business_start_date</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>06/19/2024</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t># ===== operating_model_json  (36 fields) =====</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>units_per_week_capacity</t>
+          <t>operating_model_json.consumer_type</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>consumer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>utilization_rate</t>
+          <t>operating_model_json.business_type</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Donut Shop</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t># --- example stress edit: uncomment by removing the '#' and set a value ---</t>
+          <t>operating_model_json.business_stage</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>operating</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t># cash_on_hand</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>20000</t>
+          <t>operating_model_json.business_description_summary</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Sunny Glaze Donuts is a single-location retail donut shop that produces freshly made classic and specialty donuts each morning and sells them directly to walk-in customers. The core unit of work is one donut sold, and operations are planned on a weekly cadence, targeting around 1,200 donut per period at full capacity, with practical Year-1 volume assumed at  of that level. Customers pay by cash or card at the counter, receive same-day product for immediate in-person pickup, and there is no delivery or wholesale channel in the current model. Day-to-day fulfillment is handled by the owner and shop staff, who prep dough, proof, fry, and glaze on-site before and during morning hours, then serve customers at the front counter through early afternoon. Capacity is primarily constrained by labor and in-shop equipment rather than delivery logistics or long-distance shipping, and pricing is modeled as a single average $2 per donut for planning. The business operates locally, focusing on consistent routines and a tight menu to keep output reliable and waste low. LLC status is used for liability and administrative structure, and it is assumed that all standard food-service requirements (such as health department permits, food handler certifications, and appropriate insurance) for this business type and location are identified and integrated into operations, recognizing that exact rules and licenses vary by jurisdiction and may need periodic review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].lob_name</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Primary line of business</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].product_name</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_name</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_description</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>one freshly made classic or specialty donut sold to a walk-in customer at the shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_cadence</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].units_per_week_capacity</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].units_per_period_capacity</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].operating_periods_per_year</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].utilization_rate</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_price</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>operating_model_json.unit_name</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>operating_model_json.unit_description</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>one freshly made classic or specialty donut sold to a walk-in customer at the shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>operating_model_json.unit_cadence</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>operating_model_json.units_per_week_capacity</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>operating_model_json.units_per_period_capacity</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>operating_model_json.operating_periods_per_year</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>operating_model_json.utilization_rate</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>operating_model_json.unit_price</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>operating_model_json.shipping_method</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>in-person pickup at counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>operating_model_json.sales_modality</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>operating_model_json.geographic_scope</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>operating_model_json.geographic_coverage</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Springfield and nearby communities in Sangamon County, IL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>operating_model_json.countries[0]</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>operating_model_json.milestones[0].description</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Consistently sell around 1,000 donuts per week</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>operating_model_json.milestones[0].timing</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Within the next 12 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>operating_model_json.milestones[0].timing_months_max</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>operating_model_json.capacity_driver</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>operating_model_json.primary_growth_lever</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>operating_model_json.legal_entity</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>operating_model_json.confidence</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>operating_model_json.competitive_advantage</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Sunny Glaze’s competitive advantage is a small, consistent donut menu made fresh daily at a single location, which enables high product quality, strong operational efficiency, and minimal waste compared with larger or more varied donut shops.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>operating_model_json.business_naics_6</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>311811</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t># ===== target_market_json  (30 fields) =====</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>target_market_json.consumer_type</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>target_market_json.gender_age_intent[0].gender_focus</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>target_market_json.gender_age_intent[0].age_min</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>target_market_json.gender_age_intent[0].age_max</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>target_market_json.income_intent[0].income_min</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>target_market_json.income_intent[0].income_max</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[0].segment</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[0].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>B15003_017E</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[0].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>B15003_022E</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[0].acs_codes[2]</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>B15003_023E</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[0].acs_codes[3]</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>B15003_025E</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[1].segment</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Household Structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[1].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>B11001_002E</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[1].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>B11001_007E</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[2].segment</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Housing Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[2].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>B25001_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[2].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>B25064_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[2].acs_codes[2]</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>B25077_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[3].segment</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[3].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>B23025_003E</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[3].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>B23025_004E</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[3].acs_codes[2]</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>B23025_005E</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[4].segment</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>Housing Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>target_market_json.selections[4].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>B25001_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>target_market_json.b2b_industry_terms</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>target_market_json.b2b_naics_6</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>target_market_json.b2b_size_bands</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>target_market_json.b2b_age_bands</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>target_market_json.marketing_plan_summary</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Sunny Glaze Donuts is positioned as a neighborhood, mid-market donut shop offering freshly made classic and specialty donuts at roughly $2 per donut to local adults across Springfield and nearby Sangamon County communities. The business operates on a per-visit, walk-in retail model with no delivery, and capacity is primarily constrained by in-shop labor and equipment rather than demand. Marketing emphasis will be on adults aged 18–45 in roughly $35,000–$75,000 household income brackets, especially nearby office workers and shift workers who want a quick, affordable breakfast or snack on their way to or from work, while remaining welcoming to all adult customers regardless of education level.
+Acquisition will be built around five primary channels: Google Maps/Business Profile, to capture local search intent from people nearby looking for donuts or breakfast; Google Search, to reach residents searching for donut shops or coffee-and-donut options in Springfield; Instagram, to showcase fresh donuts, daily specials, and behind-the-scenes baking that appeal to younger adults and office staff; Facebook, to reach a broad local audience for promotions, community engagement, and word-of-mouth sharing; and local referral partners such as nearby offices, clinics, and workplaces, where simple in-person outreach and occasional treat drops can convert nearby workers into regulars. This narrative defines the strategic marketing architecture and will be expanded into a detailed execution-level marketing plan in the full written business plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>target_market_json.confidence</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t># ===== people_json  (36 fields) =====</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>people_json.people[0].full_name</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>people_json.people[0].role_title</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>Owner and Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>people_json.people[0].primary_responsibilities</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Oversees all day-to-day operations of the shop including staffing, scheduling, inventory ordering, vendor relationships, cash handling, customer service, and compliance with health and safety regulations; leads planning for production targets, pricing, and promotions to meet weekly donut volume and revenue goals; manages bookkeeping and coordinates with external advisors for taxes, licensing, and insurance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>people_json.people[0].relevant_background</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>8 years of food service and retail management experience including running a small bakery; Food Safety Manager certification; completed business courses at community college</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>people_json.people[0].experience_years</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>people_json.people[0].why_strengthens_business</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Jordan brings hands-on bakery management experience, formal food safety credentials, and basic business training, giving Sunny Glaze Donuts an owner-operator who can both execute daily production and run the front-of-house while keeping costs, compliance, and quality under control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>people_json.people[0].paragraph</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Lee serves as Owner and Manager, providing end-to-end oversight of Sunny Glaze Donuts from dough production through cash-out at the register. With 8 years of food service and retail management experience, including running a small bakery, Jordan understands the practical details of labor planning, inventory control, and opening/closing routines required to consistently hit weekly donut production targets. Their Food Safety Manager certification and business coursework at community college support compliant, disciplined operations, ensuring the shop meets health standards while maintaining tight control over margins, staffing, and customer experience—critical capabilities for a single-location donut shop to operate reliably and scale steady weekly volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>people_json.people[0].annual_wage</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>75820</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>people_json.people[0].wage_source</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>oews_median</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>people_json.people[1].full_name</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>people_json.people[1].role_title</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Lead Baker</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>people_json.people[1].primary_responsibilities</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Leads daily dough preparation, proofing, frying, and glazing; sets and maintains recipes, batches, and production timing to align with target volumes; trains and oversees any assisting kitchen staff to maintain product consistency and food safety; collaborates with the owner on menu planning and daily specials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>people_json.people[1].relevant_background</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>5 years of bakery and pastry experience, including 2 years at a well-known local pastry shop; Culinary Arts diploma from the city culinary institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>people_json.people[1].experience_years</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>people_json.people[1].why_strengthens_business</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Maria’s focused bakery and pastry background, combined with formal culinary training, gives Sunny Glaze Donuts the technical production leadership needed to turn early-morning prep into consistent, high-quality donuts at the planned weekly volumes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>people_json.people[1].paragraph</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez is the Lead Baker responsible for executing the daily production engine that underpins Sunny Glaze Donuts. Drawing on 5 years of bakery and pastry experience, including time at a well-known local pastry shop, and a Culinary Arts diploma from the city culinary institute, Maria manages dough prep, proofing, frying, and glazing to deliver a reliable mix of classic and specialty donuts each morning. Her technical skills and attention to process allow the shop to run tight, repeatable production routines that protect product quality and minimize waste, ensuring the kitchen can support the planned weekly donut volumes without overextending equipment or staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>people_json.people[1].annual_wage</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>36550</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>people_json.people[1].wage_source</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>oews_median</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[0].role_title</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Front Counter Associate / Barista</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[0].annual_wage</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>34520</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[0].wage_source</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>oews_median</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[0].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[0].notes</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Needed to handle morning and midday customer service, order-taking, payment processing, and basic beverage prep so the owner and lead baker can stay focused on production and management during busy periods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[1].role_title</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Part-Time Baker / Prep Assistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[1].annual_wage</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>36550</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[1].wage_source</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>oews_median</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[1].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[1].notes</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Adds early-morning prep and frying capacity to support approaching 1,000 donuts per week without overloading the lead baker, and provides coverage for days off or unexpected demand spikes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[2].role_title</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Part-Time Marketing and Community Outreach Assistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[2].annual_wage</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>72630</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[2].wage_source</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>oews_median</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[2].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles[2].notes</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Helps maintain social media, keep the Google Business Profile updated, and coordinate simple outreach to nearby offices and workplaces as regular demand stabilizes and the team wants to deepen local awareness without pulling the owner off operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles_summary</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Suggested year-1 roles and estimated annual wages:
+- Front Counter Associate / Barista: $34,520/year (in ~0 months) - Needed to handle morning and midday customer service, order-taking, payment processing, and basic beverage prep so the owner and lead baker can stay focused on production and management during busy periods.
+- Part-Time Baker / Prep Assistant: $36,550/year (in ~6 months) - Adds early-morning prep and frying capacity to support approaching 1,000 donuts per week without overloading the lead baker, and provides coverage for days off or unexpected demand spikes.
+- Part-Time Marketing and Community Outreach Assistant: $72,630/year (in ~9 months) - Helps maintain social media, keep the Google Business Profile updated, and coordinate simple outreach to nearby offices and workplaces as regular demand stabilizes and the team wants to deepen local awareness without pulling the owner off operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>people_json.business_naics_6</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>311811</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>people_json.confidence</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t># ===== financials_json  (66 fields) =====</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>financials_json._financials_revenue_intro_done</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>financials_json.baseline_cogs_percent</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>financials_json.baseline_cogs</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="n">
+        <v>27144</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>financials_json.cogs_adjustment</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>financials_json.cogs_total_year1</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="n">
+        <v>27144</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>financials_json.cogs_basis_naics</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>311811</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>financials_json.cogs_basis_rationale</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>A small, single-location donut shop selling in person typically has direct fulfillment costs dominated by ingredients, packaging, and incremental utilities tied to production. For a $2 donut, common bakery cost structures put flour, sugar, fats, fillings, toppings, yeast, etc. at roughly 15–20% of sales when recipes and portioning are tight. Packaging (boxes, bags, napkins) often adds 4–6% at this price point, and fryer oil, gas/electricity, and cleaning/sanitation consumables add another ~4–6% on a per-unit basis. Labor is treated as operating expense rather than COGS here, since roles listed (owner/manager, lead baker, counter staff) are part of the broader operating team rather than being modeled strictly as variable, per-donut fulfillment cost. Given the shop’s focus on a small, efficient menu and reduced waste, it is reasonable to land toward the lower-middle of typical donut-shop direct cost ratios. That yields an estimated Year-1 direct COGS of about 29% of revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>financials_json.current_cogs</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="n">
+        <v>27144</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>financials_json.cogs_percent_of_revenue</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>financials_json.baseline_payroll_year1</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="n">
+        <v>183322.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_adjustment</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_total_year1</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v>183322.5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[0].source</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[0].full_name</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[0].role_title</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>Owner and Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[0].annual_wage</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="n">
+        <v>75820</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[0].months_counted_year1</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[0].year1_payroll_amount</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="n">
+        <v>75820</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[1].source</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[1].full_name</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[1].role_title</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>Lead Baker</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[1].annual_wage</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="n">
+        <v>36550</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[1].months_counted_year1</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[1].year1_payroll_amount</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="n">
+        <v>36550</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[2].source</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>inferred_role</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[2].role_title</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>Front Counter Associate / Barista</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[2].annual_wage</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="n">
+        <v>34520</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[2].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[2].months_counted_year1</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[2].year1_payroll_amount</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="n">
+        <v>34520</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[3].source</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>inferred_role</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[3].role_title</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>Part-Time Baker / Prep Assistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[3].annual_wage</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="n">
+        <v>36550</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[3].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[3].months_counted_year1</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[3].year1_payroll_amount</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="n">
+        <v>18275</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[4].source</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>inferred_role</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[4].role_title</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>Part-Time Marketing and Community Outreach Assistant</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[4].annual_wage</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="n">
+        <v>72630</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[4].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[4].months_counted_year1</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_basis_people_roles[4].year1_payroll_amount</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="n">
+        <v>18157.5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>financials_json.current_payroll</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="n">
+        <v>183322.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>financials_json.baseline_marketing_percent</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>financials_json.baseline_marketing</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="n">
+        <v>6552.000000000001</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>financials_json.marketing_adjustment</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>financials_json.marketing_total_year1</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="n">
+        <v>6552.000000000001</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>financials_json.marketing_percent_of_revenue</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>financials_json.monthly_rent_expense</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>financials_json.future_rent_expected</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>financials_json.owner_compensation</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>financials_json.other_operating_expense</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>financials_json.current_num_employees</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>financials_json.initial_assets</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>financials_json.ap_balance</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>financials_json.current_capex</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>financials_json.initial_lease</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>0,none</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>financials_json.initial_equity</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>financials_json.total_debt_outstanding</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>financials_json.other_monthly_debt_payments</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>financials_json.annual_interest_payment</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>financials_json.annual_principal_payment</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>financials_json.cash_on_hand</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>financials_json.ar_balance</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>financials_json.inventory_balance</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>financials_json.current_revenue</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t># ===== financials_year1_json  (16 fields) =====</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].lob_name</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>Primary line of business</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].product_name</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].unit_name</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].unit_description</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>one freshly made classic or specialty donut sold to a walk-in customer at the shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].unit_cadence</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].unit_price</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].units_per_week_capacity</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].units_per_period_capacity</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].operating_periods_per_year</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].utilization_rate</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].avg_units_per_period_year1</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].avg_units_per_week_year1</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].operating_weeks_per_year</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].products[0].revenue_total_year1</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="n">
+        <v>242424</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>financials_year1_json.lobs[0].revenue_total_year1</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="n">
+        <v>242424</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>financials_year1_json.company_revenue_total_year1</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="n">
+        <v>242424</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t># ===== marketing_model_json  (53 fields) =====</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>marketing_model_json.ready</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>marketing_model_json.version</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>marketing_model_json.signature</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>{"business": {"address_country": "USA", "address_state": "IL", "address_zip": "62704"}, "market": {"b2b_age_bands": [], "b2b_naics_6": [], "b2b_size_bands": [], "consumer_type": "consumer", "marketing_plan_summary": "Sunny Glaze Donuts is positioned as a neighborhood, mid-market donut shop offering freshly made classic and specialty donuts at roughly $2 per donut to local adults across Springfield and nearby Sangamon County communities. The business operates on a per-visit, walk-in retail model with no delivery, and capacity is primarily constrained by in-shop labor and equipment rather than demand. Marketing emphasis will be on adults aged 18–45 in roughly $35,000–$75,000 household income brackets, especially nearby office workers and shift workers who want a quick, affordable breakfast or snack on their way to or from work, while remaining welcoming to all adult customers regardless of education level.\n\nAcquisition will be built around five primary channels: Google Maps/Business Profile, to capture local search intent from people nearby looking for donuts or breakfast; Google Search, to reach residents searching for donut shops or coffee-and-donut options in Springfield; Instagram, to showcase fresh donuts, daily specials, and behind-the-scenes baking that appeal to younger adults and office staff; Facebook, to reach a broad local audience for promotions, community engagement, and word-of-mouth sharing; and local referral partners such as nearby offices, clinics, and workplaces, where simple in-person outreach and occasional treat drops can convert nearby workers into regulars. This narrative defines the strategic marketing architecture and will be expanded into a detailed execution-level marketing plan in the full written business plan.", "selections": [{"acs_codes": ["B15003_017E", "B15003_022E", "B15003_023E", "B15003_025E"], "segment": "Education"}, {"acs_codes": ["B11001_002E", "B11001_007E"], "segment": "Household Structure"}, {"acs_codes": ["B25001_001E", "B25064_001E", "B25077_001E"], "segment": "Housing Economics"}, {"acs_codes": ["B23025_003E", "B23025_004E", "B23025_005E"], "segment": "Employment"}, {"acs_codes": ["B25001_001E"], "segment": "Housing Economics"}], "target_market_summary": ""}, "ops": {"business_naics_6": "311811", "business_type": "Donut Shop", "capacity_driver": "labor", "competitive_advantage": "Sunny Glaze’s competitive advantage is a small, consistent donut menu made fresh daily at a single location, which enables high product quality, strong operational efficiency, and minimal waste compared with larger or more varied donut shops.", "consumer_type": "consumer", "countries": ["USA"], "geographic_coverage": "Springfield and nearby communities in Sangamon County, IL", "geographic_scope": "local", "operating_periods_per_year": 52, "primary_growth_lever": "", "sales_modality": "physical", "shipping_method": "in-person pickup at counter", "unit_cadence": "weekly", "unit_description": "one freshly made classic or specialty donut sold to a walk-in customer at the shop", "unit_name": "donut", "unit_price": 2, "units_per_period_capacity": 1200, "units_per_week_capacity": 1200, "utilization_rate": 0.75}, "year1": {"company_revenue_total_year1": 242424.0, "lobs": [{"lob_name": "Primary line of business", "products": [{"avg_units_per_period_year1": 900.0, "avg_units_per_week_year1": 900.0, "operating_periods_per_year": 52.0, "operating_weeks_per_year": 52.0, "product_name": "donut", "revenue_total_year1": 242424.0, "unit_cadence": "weekly", "unit_description": "one freshly made classic or specialty donut sold to a walk-in customer at the shop", "unit_name": "donut", "unit_price": 5.18, "units_per_period_capacity": 1200.0, "units_per_week_capacity": 1200.0, "utilization_rate": 0.75}], "revenue_total_year1": 242424.0}]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>marketing_model_json.geography_basis.scope</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>marketing_model_json.geography_basis.anchor_zip</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>62704</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>marketing_model_json.geography_basis.state_fips[0]</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>marketing_model_json.geography_basis.county_geoids[0]</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>17167</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>marketing_model_json.geography_basis.coverage_summary</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Springfield and nearby communities in Sangamon County, IL</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[0].segment</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[0].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>B15003_017E</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[0].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>B15003_022E</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[0].acs_codes[2]</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>B15003_023E</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[0].acs_codes[3]</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>B15003_025E</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[0].basis_count</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="n">
+        <v>76429.00069999999</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[0].weight_basis</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[1].segment</t>
+        </is>
+      </c>
+      <c r="B217" s="7" t="inlineStr">
+        <is>
+          <t>Household Structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[1].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>B11001_002E</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[1].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>B11001_007E</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[1].basis_count</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="n">
+        <v>83900.48809999999</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[1].weight_basis</t>
+        </is>
+      </c>
+      <c r="B221" s="7" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[2].segment</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>Housing Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[2].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>B25001_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[2].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B224" s="7" t="inlineStr">
+        <is>
+          <t>B25064_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[2].acs_codes[2]</t>
+        </is>
+      </c>
+      <c r="B225" s="7" t="inlineStr">
+        <is>
+          <t>B25077_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[2].basis_count</t>
+        </is>
+      </c>
+      <c r="B226" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[2].weight_basis</t>
+        </is>
+      </c>
+      <c r="B227" s="7" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[3].segment</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>Employment</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[3].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>B23025_003E</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[3].acs_codes[1]</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>B23025_004E</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[3].acs_codes[2]</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>B23025_005E</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[3].basis_count</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="n">
+        <v>195029.9338</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[3].weight_basis</t>
+        </is>
+      </c>
+      <c r="B233" s="7" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[4].segment</t>
+        </is>
+      </c>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t>Housing Economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[4].acs_codes[0]</t>
+        </is>
+      </c>
+      <c r="B235" s="7" t="inlineStr">
+        <is>
+          <t>B25001_001E</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[4].basis_count</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="n">
+        <v>92885.20419999999</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>marketing_model_json.b2c_basis_counts[4].weight_basis</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>marketing_model_json.reachable_market</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>marketing_model_json.market_basis_type</t>
+        </is>
+      </c>
+      <c r="B239" s="7" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>marketing_model_json.baseline_marketing</t>
+        </is>
+      </c>
+      <c r="B240" s="7" t="n">
+        <v>6552.000000000001</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>marketing_model_json.capture_rate_year1</t>
+        </is>
+      </c>
+      <c r="B241" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>marketing_model_json.marketing_intensity</t>
+        </is>
+      </c>
+      <c r="B242" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>marketing_model_json.expected_units_year1</t>
+        </is>
+      </c>
+      <c r="B243" s="7" t="n">
+        <v>46800</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>marketing_model_json.marketing_adjustment</t>
+        </is>
+      </c>
+      <c r="B244" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>marketing_model_json.reachable_market_b2b</t>
+        </is>
+      </c>
+      <c r="B245" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>marketing_model_json.reachable_market_b2c</t>
+        </is>
+      </c>
+      <c r="B246" s="7" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>marketing_model_json.required_units_year1</t>
+        </is>
+      </c>
+      <c r="B247" s="7" t="n">
+        <v>46800</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>marketing_model_json.marketing_total_year1</t>
+        </is>
+      </c>
+      <c r="B248" s="7" t="n">
+        <v>6552.000000000001</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>marketing_model_json.required_revenue_year1</t>
+        </is>
+      </c>
+      <c r="B249" s="7" t="n">
+        <v>242424</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>marketing_model_json.marketing_basis_summary</t>
+        </is>
+      </c>
+      <c r="B250" s="7" t="inlineStr">
+        <is>
+          <t>Sunny Glaze is a single-location, walk-in donut shop with purely local, in-person pickup and no delivery, so the realistic Year-1 audience is a subset of nearby adults who both live/work within easy driving distance and buy donuts at least occasionally.
+B2C narrowing: The ACS adult and employed-population bases in Sangamon County are in the ~75k–195k range, but only a fraction are realistic donut buyers for a single shop. First narrow to adults 18–64 who either live or work within roughly a 10–15 minute drive of the shop (a practical radius for a quick breakfast stop), then further to those who buy sweet baked goods or fast breakfast on-the-go. From that behavior-defined group, only a portion will discover, try, and like Sunny Glaze in Year 1. A practical planning assumption is a reachable pool on the order of ~8,000 adults who are truly in-range and behaviorally likely to buy donuts at least occasionally.
+Demand vs. reach: Year-1 required units are 46,800 donuts (900/week at 52 weeks). If we assume about 1,600 distinct customers over the year (a realistic number for a neighborhood shop), each customer would buy on average ~29 donuts/year, which could look like, for example, one 3–4 donut purchase per month or several smaller visits for some and larger office buys for others. Against a reachable local audience of ~8,000 people, that implies selling roughly 5.85 units per reachable person per year on average. This is not a literal 585% market adoption; it reflects repeat purchases and multiple donuts per visit from a smaller active subset of that reachable pool.
+Marketing intensity and percent of revenue: This is a pre-revenue, early local food-service concept where awareness and habit formation matter, but where foot traffic can be built significantly through organic discovery (Google Maps, signage), word-of-mouth, and low-cost social media. Paid advertising will likely be modest (some boosted posts, occasional local promos) compared with labor, rent, and ingredients. Given the $242k Year-1 revenue, a baseline marketing allocation around 8% of revenue (~$19k) is realistic: enough to fund ongoing social content, light paid search/social, basic photography/printing, and occasional treat drops/partner outreach, without overspending relative to a single-unit shop’s capacity.
+No B2B component: While there may be informal workplace referrals and occasional bulk orders from offices or clinics, these are still individual consumer transactions at the counter, not structured B2B accounts. Therefore reachable_market_b2b is set to 0, and the combined reachable_market figure of 8,000 is strictly people-based and used only as a planning/reporting view rather than a literal TAM count at the county level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>marketing_model_json.baseline_marketing_percent</t>
+        </is>
+      </c>
+      <c r="B251" s="7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>marketing_model_json.marketing_percent_of_revenue</t>
+        </is>
+      </c>
+      <c r="B252" s="7" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>marketing_model_json.demand_supports_required_units</t>
+        </is>
+      </c>
+      <c r="B253" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>marketing_model_json.expected_customers_or_clients_year1</t>
+        </is>
+      </c>
+      <c r="B254" s="7" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="inlineStr">
+        <is>
+          <t># ===== fulfillment_json  (2 fields) =====</t>
+        </is>
+      </c>
+      <c r="B255" s="6" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>fulfillment_json.time</t>
+        </is>
+      </c>
+      <c r="B256" s="7" t="inlineStr">
+        <is>
+          <t>same-day, immediate pickup at the counter during store hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>fulfillment_json.personnel</t>
+        </is>
+      </c>
+      <c r="B257" s="7" t="inlineStr">
+        <is>
+          <t>owner and shop staff prepare donuts and serve customers at the counter</t>
         </is>
       </c>
     </row>

--- a/Test Files/intake_bypass_scenarios.xlsx
+++ b/Test Files/intake_bypass_scenarios.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-57720" yWindow="1545" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="2" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-57720" yWindow="1545" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="4" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="_README" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,16 +15,17 @@
     <sheet name="New_Business" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Ironwood_Precision" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Maple_Grove_Dental" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Golden_Ring_Donuts" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,17 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -76,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,6 +105,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -732,6 +753,1526 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B136"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>blank_business</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t># ===== draft (business identity / address) =====</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>draft.business_name</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Golden Ring Donuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>draft.business_address</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>3120 SE Belmont St, Portland, OR 97214, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>draft.address_street</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>3120 SE Belmont St</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>draft.address_city</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>draft.address_state</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>draft.address_zip</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>97214</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>draft.address_country</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>draft.business_start_date</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t># ===== operating_model_json =====</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>operating_model_json.consumer_type</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>b2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>operating_model_json.business_type</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Retail donut shop and coffee bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>operating_model_json.business_stage</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>operating</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>operating_model_json.business_description_summary</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Neighborhood donut shop frying made-from-scratch donuts all day, paired with a full espresso and coffee bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>operating_model_json.competitive_advantage</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Made-from-scratch donuts fried fresh throughout the day with a rotating specialty menu and strong coffee attach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>operating_model_json.geographic_scope</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>operating_model_json.geographic_coverage</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Southeast Portland neighborhoods</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>operating_model_json.primary_growth_lever</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>daily_transactions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>operating_model_json.capacity_driver</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>facility</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>operating_model_json.business_naics_6</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>311811</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>operating_model_json.unit_name</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>operating_model_json.unit_price</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>operating_model_json.units_per_week_capacity</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>6004.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>operating_model_json.units_per_period_capacity</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>operating_model_json.utilization_rate</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>operating_model_json.operating_periods_per_year</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>operating_model_json.initial_assets</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>operating_model_json.initial_equity</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>operating_model_json.initial_lease</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>operating_model_json.total_debt_outstanding</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].lob_name</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Donuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].product_name</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_name</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_description</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>one freshly fried classic or specialty donut sold to a walk-in customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_cadence</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].units_per_week_capacity</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>6004.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].units_per_period_capacity</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].operating_periods_per_year</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].utilization_rate</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[0].products[0].unit_price</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].lob_name</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Coffee &amp; Beverages</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].product_name</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Beverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].unit_name</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>beverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].unit_description</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>one brewed coffee, espresso drink, or cold beverage sold to a customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].unit_cadence</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].units_per_week_capacity</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>1524.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].units_per_period_capacity</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].operating_periods_per_year</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].utilization_rate</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>operating_model_json.lob_models[1].products[0].unit_price</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>operating_model_json.shipping_method</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>in-person pickup at counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>operating_model_json.sales_modality</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>in_person</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>operating_model_json.countries[0]</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>operating_model_json.legal_entity</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>operating_model_json.confidence</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t># ===== target_market_json =====</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>target_market_json.consumer_type</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>b2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>target_market_json.marketing_plan_summary</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Local social and foot traffic, weekend specialty drops, wholesale to nearby cafes, and word of mouth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>target_market_json.confidence</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>target_market_json.gender_age_intent</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>(null)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>target_market_json.income_intent</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>(null)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t># ===== people_json =====</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>people_json.business_naics_6</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>311811</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>people_json.confidence</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>people_json.inferred_roles_summary</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Owner-baker led shop: overnight bakers plus counter and barista staff across a 7-person crew (several part-time).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>people_json.people[0].full_name</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Marcus Delgado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>people_json.people[0].role_title</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Owner / Head Baker</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>people_json.people[0].primary_responsibilities</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Recipes, overnight production, sourcing, and running the shop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>people_json.people[0].relevant_background</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>15 years baking; opened two donut concepts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>people_json.people[0].experience_years</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>people_json.people[0].why_strengthens_business</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Product quality and signature menu are the whole draw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>people_json.people[0].paragraph</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Marcus owns the recipes and the fry line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>people_json.people[0].annual_wage</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>people_json.people[0].wage_source</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>client_override</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>people_json.people[0].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>people_json.people[1].full_name</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Nina Alvarez</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>people_json.people[1].role_title</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Lead Baker</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>people_json.people[1].primary_responsibilities</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Early production runs, doughs, and consistency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>people_json.people[1].relevant_background</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>8 years baking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>people_json.people[1].experience_years</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>people_json.people[1].why_strengthens_business</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>Keeps the case full and consistent every morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>people_json.people[1].paragraph</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Nina runs the overnight bake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>people_json.people[1].annual_wage</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>people_json.people[1].wage_source</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>client_override</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>people_json.people[1].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>people_json.people[2].full_name</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Theo Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>people_json.people[2].role_title</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Baker / Fryer</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>people_json.people[2].primary_responsibilities</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Frying, glazing, and finishing donuts through the day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>people_json.people[2].relevant_background</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>5 years baking/frying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>people_json.people[2].experience_years</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>people_json.people[2].why_strengthens_business</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Fresh-all-day frying keeps quality and waste in check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>people_json.people[2].paragraph</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Theo keeps hot donuts coming out midday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>people_json.people[2].annual_wage</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>people_json.people[2].wage_source</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>client_override</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>people_json.people[2].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>people_json.people[3].full_name</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Jasmine Cole</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>people_json.people[3].role_title</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Counter Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>people_json.people[3].primary_responsibilities</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Opening, sales, customer service, and training counter staff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>people_json.people[3].relevant_background</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>4 years food-service retail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>people_json.people[3].experience_years</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>people_json.people[3].why_strengthens_business</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>Fast, friendly service drives repeat and attach sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>people_json.people[3].paragraph</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Jasmine runs front-of-house.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>people_json.people[3].annual_wage</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>people_json.people[3].wage_source</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>client_override</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>people_json.people[3].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>people_json.people[4].full_name</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>Diego Ramos</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>people_json.people[4].role_title</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>Barista / Counter Associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>people_json.people[4].primary_responsibilities</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>Coffee/espresso, register, and counter service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>people_json.people[4].relevant_background</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>3 years barista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>people_json.people[4].experience_years</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>people_json.people[4].why_strengthens_business</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Coffee attach lifts average ticket on every donut sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>people_json.people[4].paragraph</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Diego runs the coffee bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>people_json.people[4].annual_wage</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>people_json.people[4].wage_source</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>client_override</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>people_json.people[4].months_until_hire</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t># ===== financials_json =====</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>financials_json.cogs_percent_of_revenue</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>financials_json.payroll_total_year1</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="n">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>financials_json.current_revenue</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="n">
+        <v>517140</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>financials_json.cash_on_hand</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="n">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>financials_json.initial_assets</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>financials_json.initial_equity</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>financials_json.initial_lease</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>financials_json.total_debt_outstanding</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>financials_json.other_operating_expense</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>financials_json.marketing_total_year1</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>financials_json.monthly_rent_expense</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>financials_json.current_capex</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>financials_json.current_cogs</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="n">
+        <v>144799</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>financials_json.current_payroll</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="n">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>financials_json.current_num_employees</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t># ===== financials_year1_json  (recomputed - leave empty) =====</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t># ===== marketing_model_json  (recomputed - leave empty) =====</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="12" t="inlineStr">
+        <is>
+          <t># ===== fulfillment_json  (recomputed - leave empty) =====</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
